--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564384036</v>
+        <v>46157.93084801553</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93084801553</v>
+        <v>46157.93163009108</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93163009108</v>
+        <v>46157.93396498192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396498192</v>
+        <v>46157.93713802877</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713802877</v>
+        <v>46158.28212928287</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212928287</v>
+        <v>46158.29674137013</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674137013</v>
+        <v>46158.29810500667</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810500667</v>
+        <v>46158.33383818117</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383818117</v>
+        <v>46158.36852314579</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852314579</v>
+        <v>46158.37283963581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
